--- a/data/argentina/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/argentina/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>noM4eJv9</t>
+          <t>fotMKZ7K</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -462,19 +462,19 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>xvR2CVDc</t>
+          <t>YgyxEvnR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>xYveDhra</t>
+          <t>nozaSkhA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nkx6zI2q</t>
+          <t>YHCv8dOE</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -483,19 +483,19 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2RU5F8AC</t>
+          <t>KfMnPVA4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>p4iHBcGk</t>
+          <t>GW9jvbG8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pdWqnF1e</t>
+          <t>llkWcC07</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -504,19 +504,19 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Czp8uYzj</t>
+          <t>YXLYMqz6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MkIVfIHA</t>
+          <t>KAydqpwC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vq1qlyXr</t>
+          <t>hMeNaYVf</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -525,19 +525,19 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>W8lomLn5</t>
+          <t>8WPFLu92</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KfMnPVA4</t>
+          <t>UL3R30aD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>U9B9fwfF</t>
+          <t>trGn6zgR</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -546,19 +546,19 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
+          <t>xvR2CVDc</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>SdHeJ5BT</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>hhp5qLl8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KvUIXFn2</t>
+          <t>badJ0EGl</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -567,19 +567,19 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8rrQkbdH</t>
+          <t>xYveDhra</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>xIZruiA3</t>
+          <t>IFbJwyX4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bPuAZyIk</t>
+          <t>2iHr7GwL</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -588,19 +588,19 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2Z11gzUL</t>
+          <t>fVnsh4kN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>INpzsZkg</t>
+          <t>tdzQkXt9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>tlVEYeXe</t>
+          <t>WCfRbho1</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -614,14 +614,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>YXLYMqz6</t>
+          <t>r9zDZa4I</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>xzFHhHOR</t>
+          <t>vJVmoZG1</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -630,19 +630,19 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KfMnPVA4</t>
+          <t>YgyxEvnR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>fVnsh4kN</t>
+          <t>6ueHTT9o</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rDFDgc9L</t>
+          <t>fRDz9x98</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -651,19 +651,19 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>tdzQkXt9</t>
+          <t>IPCvd5Pa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>zTfUpJig</t>
+          <t>W8lomLn5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>U9kvubfS</t>
+          <t>hMZipgW7</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -672,19 +672,19 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IH9zbCEt</t>
+          <t>MkIVfIHA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>YgyxEvnR</t>
+          <t>joU5U5WF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>jJjztvuM</t>
+          <t>nPhF1f1r</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -693,61 +693,71 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>nozaSkhA</t>
+          <t>hhp5qLl8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>joU5U5WF</t>
+          <t>xvR2CVDc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8fN0daP2</t>
+          <t>trxILFhE</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gariano a 
+  arg </t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IFbJwyX4</t>
+          <t>p4iHBcGk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8rrQkbdH</t>
+          <t>IH9zbCEt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>65Xumenk</t>
+          <t>Y9EiyTMr</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tello f 
+  arg </t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6ueHTT9o</t>
+          <t>IH9zbCEt</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>W8lomLn5</t>
+          <t>r9zDZa4I</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SvlzcWFD</t>
+          <t>fgvPVMI8</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -755,44 +765,18 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">arasa n 
+          <t xml:space="preserve">penel a 
   arg </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IH9zbCEt</t>
+          <t>xtEjMiPE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>YXLYMqz6</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ngdGLTFj</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">herrera d 
-  arg </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>xvR2CVDc</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>joU5U5WF</t>
+          <t>W8lomLn5</t>
         </is>
       </c>
     </row>
